--- a/Bill of Materials.xlsx
+++ b/Bill of Materials.xlsx
@@ -1,26 +1,192 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://imperiallondon.sharepoint.com/sites/ExternalFixator-BM2/Shared Documents/3D Printed Ex Fix _ Shared Folder/Design/iFix_3D/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="209" documentId="11_6989065581098C7D886C18D4995AAD24C4035BC0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{454A224E-F16B-4786-A835-F9965A1DE6CD}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
+  <si>
+    <t>QTY.</t>
+  </si>
+  <si>
+    <t>ITEM</t>
+  </si>
+  <si>
+    <t>PART NUMBER</t>
+  </si>
+  <si>
+    <t>PART NAME</t>
+  </si>
+  <si>
+    <t>PART DESCRIPTION</t>
+  </si>
+  <si>
+    <t>MATERIAL</t>
+  </si>
+  <si>
+    <t>UNIT COST</t>
+  </si>
+  <si>
+    <t>TOTAL COST</t>
+  </si>
+  <si>
+    <t>iFix_3D</t>
+  </si>
+  <si>
+    <t>Bill of Materials</t>
+  </si>
+  <si>
+    <t>Assembly Name</t>
+  </si>
+  <si>
+    <t>Assembly Revision</t>
+  </si>
+  <si>
+    <t>Date of Approval</t>
+  </si>
+  <si>
+    <t>Total Pieces</t>
+  </si>
+  <si>
+    <t>Total Cost</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>iFix_3D Kit</t>
+  </si>
+  <si>
+    <t>1.0.0</t>
+  </si>
+  <si>
+    <t>ABS</t>
+  </si>
+  <si>
+    <t>3D Printed Pin Clamp</t>
+  </si>
+  <si>
+    <t>3D Printed Rod Clamp</t>
+  </si>
+  <si>
+    <t>PinClamp</t>
+  </si>
+  <si>
+    <t>RodClamp</t>
+  </si>
+  <si>
+    <t>Schanz Pin</t>
+  </si>
+  <si>
+    <t>Surgical bone pin</t>
+  </si>
+  <si>
+    <t>SS 316</t>
+  </si>
+  <si>
+    <t>1/2 inch diameter, 30cm long rod</t>
+  </si>
+  <si>
+    <t>Hexagon Head Bolt</t>
+  </si>
+  <si>
+    <t>Hexagon Nut</t>
+  </si>
+  <si>
+    <t>Washer</t>
+  </si>
+  <si>
+    <t>ISO 4032, M8</t>
+  </si>
+  <si>
+    <t>Solid Rod</t>
+  </si>
+  <si>
+    <t>HYW-M8-20-A2</t>
+  </si>
+  <si>
+    <t>8mm ID, 20mm OD, 1.5mm thickness</t>
+  </si>
+  <si>
+    <t>* Costs are calculated based on a purchase quantity of 1000</t>
+  </si>
+  <si>
+    <t>* Costs therefore may be lower with higher quantities</t>
+  </si>
+  <si>
+    <t>SOURCE</t>
+  </si>
+  <si>
+    <t>Buy M8 x 20mm Penny Washers - Stainless Steel (A2) - Accu</t>
+  </si>
+  <si>
+    <t>Buy M8 Hexagon Nuts (ISO 4032) - Marine Stainless Steel (A4) - Accu</t>
+  </si>
+  <si>
+    <t>HPN-M8-V1-A4</t>
+  </si>
+  <si>
+    <t>ISO 4017, M8, 55mm length</t>
+  </si>
+  <si>
+    <t>Buy M8 x 55mm Full Thread Hexagon Bolts (ISO 4017) High Tensile Steel (A4-70) - Accu</t>
+  </si>
+  <si>
+    <t>SEBF-M8-55-A4-70</t>
+  </si>
+  <si>
+    <t>SS</t>
+  </si>
+  <si>
+    <t>image of clamp setup</t>
+  </si>
+  <si>
+    <t>* Printed costs are based on pure material costs, not including maintenance or upkeep</t>
+  </si>
+  <si>
+    <t>* Material costs are estimated based on generic pre-manufactured reels, not virgin pellets</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +194,52 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -45,17 +247,357 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color theme="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="11">
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="34" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-0.34998626667073579"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -66,6 +608,25 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{0777326A-16E4-4DBC-AD95-475962C56739}" name="Table1" displayName="Table1" ref="A10:I20" totalsRowShown="0" headerRowDxfId="10" dataDxfId="5">
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{65E79DBC-A5BE-4F63-B515-613496830B26}" name="ITEM" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{9DB7FA4A-88ED-4093-B061-5C0C279900A5}" name="MATERIAL" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{B39AB758-9318-4433-901C-B08BB7E10349}" name="PART NUMBER" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{4DB8D22F-4B25-4584-B729-3AFE7A3AF03F}" name="PART NAME" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{8527247E-F577-403B-A357-14ECD7A252FD}" name="PART DESCRIPTION" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{D2F6807B-6629-4790-864C-C75BA78715EB}" name="SOURCE" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{595FA9B7-1438-4511-91DE-11541F79997E}" name="UNIT COST" dataDxfId="3" dataCellStyle="Currency"/>
+    <tableColumn id="2" xr3:uid="{82093A87-C5F2-4280-B854-178F39AE9A60}" name="QTY." dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{D846D9CB-B336-49DD-99FE-7E1778E4F5A6}" name="TOTAL COST" dataDxfId="1" dataCellStyle="Currency">
+      <calculatedColumnFormula>Table1[[#This Row],[QTY.]]*Table1[[#This Row],[UNIT COST]]</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,15 +891,468 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.21875" customWidth="1"/>
+    <col min="2" max="2" width="14.109375" customWidth="1"/>
+    <col min="3" max="3" width="18.88671875" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" customWidth="1"/>
+    <col min="5" max="5" width="55.77734375" customWidth="1"/>
+    <col min="6" max="6" width="9.5546875" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="9.21875" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="14"/>
+    </row>
+    <row r="2" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="15"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="18"/>
+    </row>
+    <row r="3" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="10"/>
+      <c r="C4" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="28"/>
+    </row>
+    <row r="5" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="10"/>
+      <c r="C5" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="29"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="31"/>
+    </row>
+    <row r="6" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="10"/>
+      <c r="C6" s="23">
+        <v>45896</v>
+      </c>
+      <c r="E6" s="29"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="31"/>
+    </row>
+    <row r="7" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="10"/>
+      <c r="C7" s="22">
+        <f>H21</f>
+        <v>25</v>
+      </c>
+      <c r="E7" s="29"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="31"/>
+    </row>
+    <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="10"/>
+      <c r="C8" s="24">
+        <f>I21</f>
+        <v>9.48</v>
+      </c>
+      <c r="E8" s="32"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="34"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>1</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="8"/>
+      <c r="G11" s="3">
+        <v>0.41</v>
+      </c>
+      <c r="H11" s="1">
+        <v>4</v>
+      </c>
+      <c r="I11" s="3">
+        <f>Table1[[#This Row],[QTY.]]*Table1[[#This Row],[UNIT COST]]</f>
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>2</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="8"/>
+      <c r="G12" s="3">
+        <v>0.85</v>
+      </c>
+      <c r="H12" s="1">
+        <v>4</v>
+      </c>
+      <c r="I12" s="3">
+        <f>Table1[[#This Row],[QTY.]]*Table1[[#This Row],[UNIT COST]]</f>
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>3</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="8"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="1">
+        <v>4</v>
+      </c>
+      <c r="I13" s="3">
+        <f>Table1[[#This Row],[QTY.]]*Table1[[#This Row],[UNIT COST]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>4</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="8"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
+      <c r="I14" s="3">
+        <f>Table1[[#This Row],[QTY.]]*Table1[[#This Row],[UNIT COST]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>5</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.89</v>
+      </c>
+      <c r="H15" s="1">
+        <v>4</v>
+      </c>
+      <c r="I15" s="3">
+        <f>Table1[[#This Row],[QTY.]]*Table1[[#This Row],[UNIT COST]]</f>
+        <v>3.56</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>6</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="H16" s="1">
+        <v>4</v>
+      </c>
+      <c r="I16" s="3">
+        <f>Table1[[#This Row],[QTY.]]*Table1[[#This Row],[UNIT COST]]</f>
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>7</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.06</v>
+      </c>
+      <c r="H17" s="1">
+        <v>4</v>
+      </c>
+      <c r="I17" s="3">
+        <f>Table1[[#This Row],[QTY.]]*Table1[[#This Row],[UNIT COST]]</f>
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>8</v>
+      </c>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="3">
+        <f>Table1[[#This Row],[QTY.]]*Table1[[#This Row],[UNIT COST]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>9</v>
+      </c>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="3">
+        <f>Table1[[#This Row],[QTY.]]*Table1[[#This Row],[UNIT COST]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="1">
+        <v>10</v>
+      </c>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="3">
+        <f>Table1[[#This Row],[QTY.]]*Table1[[#This Row],[UNIT COST]]</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G21" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="5">
+        <f>SUM(Table1[QTY.])</f>
+        <v>25</v>
+      </c>
+      <c r="I21" s="6">
+        <f>SUM(Table1[TOTAL COST])</f>
+        <v>9.48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="E4:I8"/>
+    <mergeCell ref="D1:I2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="F17" r:id="rId1" display="https://www.accu.co.uk/metric-flat-washers/14669-HYW-M8-20-A2" xr:uid="{E2D75C01-69B5-4589-A625-71F56EB77D52}"/>
+    <hyperlink ref="F16" r:id="rId2" display="https://www.accu.co.uk/hexagon-nuts/406395-HPN-M8-V1-A4" xr:uid="{B28FF56C-3A26-40D1-A9A7-112DA4A8597E}"/>
+    <hyperlink ref="F15" r:id="rId3" display="https://www.accu.co.uk/full-thread-hexagon-bolts/630507-SEBF-M8-55-A4-70" xr:uid="{CB760D60-7F24-4FAF-AD6A-9D62B58C9AAF}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId4"/>
+  <tableParts count="1">
+    <tablePart r:id="rId5"/>
+  </tableParts>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="bd28c45f-cebe-4509-9066-0257869280d0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3e1f64af-336a-4cd0-ac0d-fe3d4e694e88">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002F51508F35EA984B89BFC0F6DE5C8782" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="62a237a457c373f5131e8eb68765dbeb">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3e1f64af-336a-4cd0-ac0d-fe3d4e694e88" xmlns:ns3="bd28c45f-cebe-4509-9066-0257869280d0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="18cc484d985d039046b6b51bb5963ae1" ns2:_="" ns3:_="">
     <xsd:import namespace="3e1f64af-336a-4cd0-ac0d-fe3d4e694e88"/>
@@ -539,34 +1553,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="bd28c45f-cebe-4509-9066-0257869280d0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="3e1f64af-336a-4cd0-ac0d-fe3d4e694e88">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2ECC93B5-18E0-478B-B004-4068AA38953F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ED96DD7-8762-43E7-B5A3-A874F4E52DF6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="bd28c45f-cebe-4509-9066-0257869280d0"/>
+    <ds:schemaRef ds:uri="3e1f64af-336a-4cd0-ac0d-fe3d4e694e88"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{015CEFCB-90FA-416F-BE20-8A29348E8212}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{015CEFCB-90FA-416F-BE20-8A29348E8212}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4ED96DD7-8762-43E7-B5A3-A874F4E52DF6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2ECC93B5-18E0-478B-B004-4068AA38953F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="3e1f64af-336a-4cd0-ac0d-fe3d4e694e88"/>
+    <ds:schemaRef ds:uri="bd28c45f-cebe-4509-9066-0257869280d0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>